--- a/Gamma distribution results.xlsx
+++ b/Gamma distribution results.xlsx
@@ -3,7 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="BIC_values" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="p_values" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="106">
   <si>
     <t>HBB</t>
   </si>
@@ -218,13 +219,124 @@
   </si>
   <si>
     <t>1.0000 380.2767</t>
+  </si>
+  <si>
+    <t>0.71020390 0.01483808</t>
+  </si>
+  <si>
+    <t>0.305689051 0.002767188</t>
+  </si>
+  <si>
+    <t>0.479150365 0.004366119</t>
+  </si>
+  <si>
+    <t>0.80806165 0.02674948</t>
+  </si>
+  <si>
+    <t>0.8689817 0.2557752</t>
+  </si>
+  <si>
+    <t>0.71641166 0.03499798</t>
+  </si>
+  <si>
+    <t>0.66013986 0.08702409</t>
+  </si>
+  <si>
+    <t>0.27541846 0.02074752</t>
+  </si>
+  <si>
+    <t>0.38024782 0.03561137</t>
+  </si>
+  <si>
+    <t>1.0000000 0.3333333</t>
+  </si>
+  <si>
+    <t>0.83258769 0.07466063</t>
+  </si>
+  <si>
+    <t>0.7301111 0.1258741</t>
+  </si>
+  <si>
+    <t>0.63548496 0.01878225</t>
+  </si>
+  <si>
+    <t>0.1 0.1</t>
+  </si>
+  <si>
+    <t>0.67813823 0.07546401</t>
+  </si>
+  <si>
+    <t>0.218368421 0.007289903</t>
+  </si>
+  <si>
+    <t>0.5881961 0.1264877</t>
+  </si>
+  <si>
+    <t>0.2145346315 0.0006700468</t>
+  </si>
+  <si>
+    <t>0.83196961 0.01229861</t>
+  </si>
+  <si>
+    <t>0.42178180 0.02472025</t>
+  </si>
+  <si>
+    <t>0.5751748 0.0530303</t>
+  </si>
+  <si>
+    <t>0.255061993 0.003967294</t>
+  </si>
+  <si>
+    <t>0.142857143 0.002164502</t>
+  </si>
+  <si>
+    <t>0.9307359 0.1428571</t>
+  </si>
+  <si>
+    <t>1.0000000 0.2285714</t>
+  </si>
+  <si>
+    <t>0.21453463 0.01119935</t>
+  </si>
+  <si>
+    <t>0.7810479 0.1323939</t>
+  </si>
+  <si>
+    <t>0.6601399 0.2826729</t>
+  </si>
+  <si>
+    <t>0.47402597 0.02597403</t>
+  </si>
+  <si>
+    <t>0.660139860 0.002486402</t>
+  </si>
+  <si>
+    <t>0.7714286 0.2285714</t>
+  </si>
+  <si>
+    <t>0.87301587 0.07936508</t>
+  </si>
+  <si>
+    <t>0.58819607 0.04427245</t>
+  </si>
+  <si>
+    <t>0.22857143 0.02857143</t>
+  </si>
+  <si>
+    <t>0.58819607 0.01264927</t>
+  </si>
+  <si>
+    <t>0.357142857 0.007936508</t>
+  </si>
+  <si>
+    <t>0.575174825 0.008158508</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -246,6 +358,10 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
       <color rgb="FF000000"/>
@@ -286,7 +402,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -305,8 +421,14 @@
     <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -317,6 +439,10 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -608,10 +734,10 @@
       <c r="H2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="6" t="s">
         <v>19</v>
       </c>
       <c r="K2" s="4" t="s">
@@ -623,13 +749,13 @@
       <c r="M2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="6" t="s">
         <v>23</v>
       </c>
     </row>
@@ -637,7 +763,7 @@
       <c r="A3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -646,16 +772,16 @@
       <c r="D3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>27</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>28</v>
       </c>
       <c r="I3" s="4" t="s">
@@ -673,13 +799,13 @@
       <c r="M3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="P3" s="6" t="s">
         <v>32</v>
       </c>
     </row>
@@ -693,25 +819,25 @@
       <c r="C4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>36</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="6" t="s">
         <v>39</v>
       </c>
       <c r="K4" s="4" t="s">
@@ -737,25 +863,25 @@
       <c r="A5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="6" t="s">
         <v>46</v>
       </c>
       <c r="I5" s="4" t="s">
@@ -793,19 +919,19 @@
       <c r="C6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="6" t="s">
         <v>52</v>
       </c>
       <c r="I6" s="4" t="s">
@@ -837,13 +963,13 @@
       <c r="A7" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>56</v>
       </c>
       <c r="E7" s="4" t="s">
@@ -855,10 +981,10 @@
       <c r="G7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="6" t="s">
         <v>58</v>
       </c>
       <c r="J7" s="4" t="s">
@@ -887,13 +1013,13 @@
       <c r="A8" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>62</v>
       </c>
       <c r="E8" s="4" t="s">
@@ -905,22 +1031,22 @@
       <c r="G8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="L8" s="5" t="s">
+      <c r="L8" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="M8" s="5" t="s">
+      <c r="M8" s="6" t="s">
         <v>68</v>
       </c>
       <c r="N8" s="4" t="s">
@@ -934,21 +1060,540 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="23.38"/>
+    <col customWidth="1" min="2" max="2" width="20.88"/>
+    <col customWidth="1" min="3" max="3" width="19.13"/>
+    <col customWidth="1" min="4" max="4" width="17.25"/>
+    <col customWidth="1" min="5" max="5" width="19.13"/>
+    <col customWidth="1" min="6" max="7" width="20.88"/>
+    <col customWidth="1" min="8" max="8" width="19.13"/>
+    <col customWidth="1" min="9" max="9" width="20.88"/>
+    <col customWidth="1" min="10" max="10" width="20.75"/>
+    <col customWidth="1" min="11" max="11" width="20.88"/>
+    <col customWidth="1" min="12" max="12" width="17.25"/>
+    <col customWidth="1" min="14" max="14" width="19.13"/>
+    <col customWidth="1" min="15" max="15" width="17.25"/>
+    <col customWidth="1" min="16" max="16" width="19.13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8">
+        <v>1.0</v>
+      </c>
+      <c r="B15" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="C15" s="8">
+        <v>3.0</v>
+      </c>
+      <c r="D15" s="8">
+        <v>4.0</v>
+      </c>
+      <c r="E15" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="F15" s="8">
+        <v>6.0</v>
+      </c>
+      <c r="G15" s="8">
+        <v>7.0</v>
+      </c>
+      <c r="H15" s="8">
+        <v>8.0</v>
+      </c>
+      <c r="I15" s="8">
+        <v>9.0</v>
+      </c>
+      <c r="J15" s="8">
+        <v>10.0</v>
+      </c>
+      <c r="K15" s="8">
+        <v>11.0</v>
+      </c>
+      <c r="L15" s="8">
+        <v>12.0</v>
+      </c>
+      <c r="M15" s="8">
+        <v>13.0</v>
+      </c>
+      <c r="N15" s="8">
+        <v>14.0</v>
+      </c>
+      <c r="O15" s="8">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
